--- a/artfynd/A 30748-2026 artfynd.xlsx
+++ b/artfynd/A 30748-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135450771</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135450772</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135450773</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135450770</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135450768</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135450769</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,8 +1481,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135450774</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30748-2026 artfynd.xlsx
+++ b/artfynd/A 30748-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135450771</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135450772</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135450773</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135450770</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135450768</v>
       </c>
       <c r="B6" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135450769</v>
       </c>
       <c r="B7" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135450774</v>
       </c>
       <c r="B8" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30748-2026 artfynd.xlsx
+++ b/artfynd/A 30748-2026 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>135450768</v>
       </c>
       <c r="B6" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135450769</v>
       </c>
       <c r="B7" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135450774</v>
       </c>
       <c r="B8" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30748-2026 artfynd.xlsx
+++ b/artfynd/A 30748-2026 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>135450768</v>
       </c>
       <c r="B6" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135450769</v>
       </c>
       <c r="B7" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135450774</v>
       </c>
       <c r="B8" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30748-2026 artfynd.xlsx
+++ b/artfynd/A 30748-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135450771</v>
       </c>
       <c r="B2" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135450772</v>
       </c>
       <c r="B3" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135450773</v>
       </c>
       <c r="B4" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135450770</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135450768</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135450769</v>
       </c>
       <c r="B7" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135450774</v>
       </c>
       <c r="B8" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
